--- a/data/tags/אלבומים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קובי פרץ - כל עולמי EP</v>
+        <v>אריק סיני – כל השירים היפים באמת</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24468&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%a7-%d7%a1%d7%99%d7%a0%d7%99-%d7%9b%d7%9c-%d7%94%d7%a9%d7%99%d7%a8%d7%99%d7%9d-%d7%94%d7%99%d7%a4%d7%99%d7%9d-%d7%91%d7%90%d7%9e%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-09</v>
+        <v>2026-05-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:35</v>
+        <v>האלבום "כל השירים היפים באמת” של אריק סיני הוא לא סתם אוסף קאברים אלא אלבום פרשנות. סיני לא מנסה “לעדכן” את השירים בכוח או להתחרות בביצועים המקוריים, אלא להפוך אותם לחלק מהעולם הפנימי והקולי שלו. זה אלבום שמבוסס פחות על</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קובי פרץ - כל עולמי EP</v>
+        <v>אריק סיני – כל השירים היפים באמת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-05-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זהו זה - עונה 8</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%99%d7%a7-%d7%a1%d7%99%d7%a0%d7%99-%d7%9b%d7%9c-%d7%94%d7%a9%d7%99%d7%a8%d7%99%d7%9d-%d7%94%d7%99%d7%a4%d7%99%d7%9d-%d7%91%d7%90%d7%9e%d7%aa/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-10</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>האלבום "כל השירים היפים באמת” של אריק סיני הוא לא סתם אוסף קאברים אלא אלבום פרשנות. סיני לא מנסה “לעדכן” את השירים בכוח או להתחרות בביצועים המקוריים, אלא להפוך אותם לחלק מהעולם הפנימי והקולי שלו. זה אלבום שמבוסס פחות על</v>
+        <v>09:37</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אריק סיני – כל השירים היפים באמת</v>
+        <v>זהו זה - עונה 8</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-05-week02/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-05-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>זהו זה - עונה 8</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24469&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%96%d7%90%d7%a8%d7%94-%d7%9c%d7%90%d7%a8%d7%a1%d7%95%d7%9f-midnight-sun/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-05-13</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>09:37</v>
+        <v>״אמרתי שעד גיל 20 אמלא אצטדיונים״,  שרה זארה לארסון ב־Midnight Sun, ואילו ב״Saturn’s Return״ אחד השרים היפים באלבום – . ״זה לא קרה, אז פשוט דחיתי את הדדליין״ השילוב המושך הזה בין נחישות לפגיעוּת זורם לאורך אלבום הדאנס־פופ המסחרר של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>זהו זה - עונה 8</v>
+        <v>זארה לארסון Midnight Sun</v>
       </c>
     </row>
   </sheetData>
